--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,87 +608,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,147 +706,147 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=850bbd121eda6f31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8797983cc7729f69</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
@@ -1022,41 +1022,6 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850bbd121eda6f31</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -775,251 +775,6 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Python Developer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8797983cc7729f69</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Lakeview Loan Servicing</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa98384834f1f2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Applix Inc.</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
         </is>
       </c>
     </row>
@@ -670,41 +670,6 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,6 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9684b1e8c83efb55</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa98384834f1f2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa98384834f1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,41 +602,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-10.xlsx
+++ b/results/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,37 +561,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Applix Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,77 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0de03440ff246ea3</t>
         </is>
       </c>
     </row>
